--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37045,7 +37045,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-01 15:38</t>
+          <t>2026-06-02 13:39</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37288,7 +37288,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-03 13:17</t>
+          <t>2026-06-03 15:06</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37531,7 +37531,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-03 16:40</t>
+          <t>2026-06-03 17:30</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37693,7 +37693,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-04 13:12</t>
+          <t>2026-06-04 13:19</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37693,7 +37693,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-04 13:19</t>
+          <t>2026-06-04 13:38</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37693,7 +37693,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-05 12:54</t>
+          <t>2026-06-05 13:31</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37855,7 +37855,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-06 12:20</t>
+          <t>2026-06-06 12:29</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -37855,7 +37855,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-06 12:29</t>
+          <t>2026-06-07 10:00</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -38098,7 +38098,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-08 20:47</t>
+          <t>2026-06-09 10:01</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -38179,7 +38179,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-09 22:49</t>
+          <t>2026-06-10 10:20</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -38827,7 +38827,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-13 10:01</t>
+          <t>2026-06-14 10:02</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -38989,7 +38989,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-15 10:01</t>
+          <t>2026-06-16 10:02</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -39232,7 +39232,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-17 10:01</t>
+          <t>2026-06-18 10:01</t>
         </is>
       </c>
     </row>

--- a/2026 Pitching Stats/mlb_pitching_stats.xlsx
+++ b/2026 Pitching Stats/mlb_pitching_stats.xlsx
@@ -39799,7 +39799,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-22 10:01</t>
+          <t>2026-06-23 10:01</t>
         </is>
       </c>
     </row>
